--- a/resources/library/xlsx/menu-pricing-calculator.xlsx
+++ b/resources/library/xlsx/menu-pricing-calculator.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" r:id="R1fc10ab9e49c4f3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R20f938c4e36a4b9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R9ca94ef1fcd24381"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" r:id="R94d8e19daec640b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R85781f411ed043e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R1cac9233c1814ba8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -176,6 +176,102 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="916a6e46-c908-48c4-8fc7-88fb0cdfdec5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R3efb205341474cd5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="7f68f6f4-b23f-449d-a156-244a95706def"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R236ac1847bb946a8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="76b9f46f-17c7-4787-aac9-79929cda2ceb"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R44f0bbf76d154fd2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -386,7 +482,7 @@
     <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12"/>
@@ -1622,6 +1718,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78e0d258390f44e9"/>
 </x:worksheet>
 </file>
 
@@ -1636,7 +1733,7 @@
     <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12"/>
@@ -2697,6 +2794,7 @@
     <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2dff183ea7943cc"/>
 </x:worksheet>
 </file>
 
@@ -2711,7 +2809,7 @@
     <x:col min="2" max="2" width="80" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12"/>
@@ -3777,5 +3875,6 @@
     <x:mergeCell ref="A5:H5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63b0d9677155480b"/>
 </x:worksheet>
 </file>